--- a/Res_ConvLSTM/DroughtDataset_model_testing_1754918674_h_5.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1754918674_h_5.xlsx
@@ -658,7 +658,7 @@
         <v>0.008414815340366153</v>
       </c>
       <c r="C2" t="n">
-        <v>31731900</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>31731900</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>23482280</v>
+        <v>4428836</v>
       </c>
       <c r="L2" t="n">
-        <v>13557983</v>
+        <v>2315221</v>
       </c>
       <c r="M2" t="n">
-        <v>3232146</v>
+        <v>528347</v>
       </c>
       <c r="N2" t="n">
-        <v>126564</v>
+        <v>16667</v>
       </c>
       <c r="O2" t="n">
-        <v>1918019</v>
+        <v>314956</v>
       </c>
       <c r="P2" t="n">
-        <v>735505</v>
+        <v>125956</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9998523592948914</v>
+        <v>0.9998550415039062</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9066476225852966</v>
+        <v>0.8432468175888062</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8202295303344727</v>
+        <v>0.7124936580657959</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7706760764122009</v>
+        <v>0.6263427138328552</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2503010928630829</v>
+        <v>0.1580139994621277</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8043515682220459</v>
+        <v>0.6840519905090332</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8864849209785461</v>
+        <v>0.7988736033439636</v>
       </c>
       <c r="X2" t="n">
-        <v>31731900</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>31731900</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>24245260</v>
+        <v>4837248</v>
       </c>
       <c r="AG2" t="n">
-        <v>14923204</v>
+        <v>2993650</v>
       </c>
       <c r="AH2" t="n">
-        <v>4005328</v>
+        <v>801659</v>
       </c>
       <c r="AI2" t="n">
-        <v>295559</v>
+        <v>59131</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2296294</v>
+        <v>459565</v>
       </c>
       <c r="AK2" t="n">
-        <v>900185</v>
+        <v>180092</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9565883278846741</v>
+        <v>0.9563066959381104</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9112817645072937</v>
+        <v>0.9114376902580261</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8580537438392639</v>
+        <v>0.8578296899795532</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6622784733772278</v>
+        <v>0.6616203784942627</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019806981086731</v>
+        <v>0.9018417000770569</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314298033714294</v>
+        <v>0.931449294090271</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002016582438865534</v>
       </c>
       <c r="C3" t="n">
-        <v>3472</v>
+        <v>696</v>
       </c>
       <c r="D3" t="n">
-        <v>23482280</v>
+        <v>4428836</v>
       </c>
       <c r="E3" t="n">
-        <v>1804043</v>
+        <v>609667</v>
       </c>
       <c r="F3" t="n">
-        <v>24086</v>
+        <v>11006</v>
       </c>
       <c r="G3" t="n">
-        <v>2926</v>
+        <v>1115</v>
       </c>
       <c r="H3" t="n">
-        <v>1092</v>
+        <v>547</v>
       </c>
       <c r="I3" t="n">
-        <v>71</v>
+        <v>17</v>
       </c>
       <c r="J3" t="n">
-        <v>50343414</v>
+        <v>10068700</v>
       </c>
       <c r="K3" t="n">
-        <v>54344192</v>
+        <v>10540829</v>
       </c>
       <c r="L3" t="n">
-        <v>62708939</v>
+        <v>12191659</v>
       </c>
       <c r="M3" t="n">
-        <v>76447668</v>
+        <v>15165686</v>
       </c>
       <c r="N3" t="n">
-        <v>81254337</v>
+        <v>16237770</v>
       </c>
       <c r="O3" t="n">
-        <v>79066614</v>
+        <v>15760823</v>
       </c>
       <c r="P3" t="n">
-        <v>81019233</v>
+        <v>16190896</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9274945855140686</v>
+        <v>0.8766701817512512</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8267292380332947</v>
+        <v>0.7036932110786438</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6920241713523865</v>
+        <v>0.5650057196617126</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2834072411060333</v>
+        <v>0.1863921582698822</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7530940175056458</v>
+        <v>0.617917001247406</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7609315514564514</v>
+        <v>0.65129554271698</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>24245260</v>
+        <v>4837248</v>
       </c>
       <c r="Z3" t="n">
-        <v>995349</v>
+        <v>199108</v>
       </c>
       <c r="AA3" t="n">
-        <v>42884</v>
+        <v>8602</v>
       </c>
       <c r="AB3" t="n">
-        <v>34102</v>
+        <v>6851</v>
       </c>
       <c r="AC3" t="n">
-        <v>225</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>50348100</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>55661737</v>
+        <v>11143104</v>
       </c>
       <c r="AG3" t="n">
-        <v>64227600</v>
+        <v>12835014</v>
       </c>
       <c r="AH3" t="n">
-        <v>76746838</v>
+        <v>15348021</v>
       </c>
       <c r="AI3" t="n">
-        <v>81482703</v>
+        <v>16296339</v>
       </c>
       <c r="AJ3" t="n">
-        <v>79283607</v>
+        <v>15856274</v>
       </c>
       <c r="AK3" t="n">
-        <v>81047145</v>
+        <v>16209353</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9576305150985718</v>
+        <v>0.957513689994812</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099767208099365</v>
+        <v>0.9098963737487793</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8575676679611206</v>
+        <v>0.8572810888290405</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6618276834487915</v>
+        <v>0.6612800359725952</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016205072402954</v>
+        <v>0.9016276001930237</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313045144081116</v>
+        <v>0.9312229752540588</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03185715663591164</v>
       </c>
       <c r="C4" t="n">
-        <v>246</v>
+        <v>59</v>
       </c>
       <c r="D4" t="n">
-        <v>2272853</v>
+        <v>778494</v>
       </c>
       <c r="E4" t="n">
-        <v>13557983</v>
+        <v>2315221</v>
       </c>
       <c r="F4" t="n">
-        <v>522104</v>
+        <v>173623</v>
       </c>
       <c r="G4" t="n">
-        <v>18652</v>
+        <v>8380</v>
       </c>
       <c r="H4" t="n">
-        <v>25869</v>
+        <v>13262</v>
       </c>
       <c r="I4" t="n">
-        <v>1838</v>
+        <v>1061</v>
       </c>
       <c r="J4" t="n">
-        <v>4686</v>
+        <v>920</v>
       </c>
       <c r="K4" t="n">
-        <v>2417838</v>
+        <v>823287</v>
       </c>
       <c r="L4" t="n">
-        <v>2971516</v>
+        <v>934241</v>
       </c>
       <c r="M4" t="n">
-        <v>961764</v>
+        <v>315196</v>
       </c>
       <c r="N4" t="n">
-        <v>379083</v>
+        <v>88811</v>
       </c>
       <c r="O4" t="n">
-        <v>466534</v>
+        <v>145471</v>
       </c>
       <c r="P4" t="n">
-        <v>94182</v>
+        <v>31711</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999261498451233</v>
+        <v>0.9999275207519531</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9169526100158691</v>
+        <v>0.85963374376297</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8234665393829346</v>
+        <v>0.7080661058425903</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7292354702949524</v>
+        <v>0.5940952897071838</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2658273577690125</v>
+        <v>0.1710339337587357</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7778793573379517</v>
+        <v>0.6493047475814819</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8189238905906677</v>
+        <v>0.7175754308700562</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1027338</v>
+        <v>206350</v>
       </c>
       <c r="Z4" t="n">
-        <v>14923204</v>
+        <v>2993650</v>
       </c>
       <c r="AA4" t="n">
-        <v>415378</v>
+        <v>83345</v>
       </c>
       <c r="AB4" t="n">
-        <v>27557</v>
+        <v>5539</v>
       </c>
       <c r="AC4" t="n">
-        <v>5728</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>340</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1100293</v>
+        <v>221012</v>
       </c>
       <c r="AG4" t="n">
-        <v>1452855</v>
+        <v>290886</v>
       </c>
       <c r="AH4" t="n">
-        <v>662594</v>
+        <v>132861</v>
       </c>
       <c r="AI4" t="n">
-        <v>150717</v>
+        <v>30242</v>
       </c>
       <c r="AJ4" t="n">
-        <v>249541</v>
+        <v>50020</v>
       </c>
       <c r="AK4" t="n">
-        <v>66270</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9571090936660767</v>
+        <v>0.9569098353385925</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106287360191345</v>
+        <v>0.9106664061546326</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8578105568885803</v>
+        <v>0.8575552701950073</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6620529890060425</v>
+        <v>0.661450207233429</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018005132675171</v>
+        <v>0.9017346501350403</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313670992851257</v>
+        <v>0.9313361048698425</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="D5" t="n">
-        <v>92773</v>
+        <v>29171</v>
       </c>
       <c r="E5" t="n">
-        <v>1026177</v>
+        <v>281358</v>
       </c>
       <c r="F5" t="n">
-        <v>3232146</v>
+        <v>528347</v>
       </c>
       <c r="G5" t="n">
-        <v>129913</v>
+        <v>27563</v>
       </c>
       <c r="H5" t="n">
-        <v>177982</v>
+        <v>62864</v>
       </c>
       <c r="I5" t="n">
-        <v>11507</v>
+        <v>5801</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1835690</v>
+        <v>623048</v>
       </c>
       <c r="L5" t="n">
-        <v>2841562</v>
+        <v>974879</v>
       </c>
       <c r="M5" t="n">
-        <v>1438422</v>
+        <v>406771</v>
       </c>
       <c r="N5" t="n">
-        <v>320016</v>
+        <v>72752</v>
       </c>
       <c r="O5" t="n">
-        <v>628833</v>
+        <v>194750</v>
       </c>
       <c r="P5" t="n">
-        <v>231080</v>
+        <v>67437</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999428987503052</v>
+        <v>0.9999439716339111</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9481782913208008</v>
+        <v>0.9118947982788086</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9291778802871704</v>
+        <v>0.8837037086486816</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9707579612731934</v>
+        <v>0.9560205340385437</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9914827346801758</v>
+        <v>0.9901582002639771</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9866548776626587</v>
+        <v>0.9792750477790833</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9960372447967529</v>
+        <v>0.9939602613449097</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>40265</v>
+        <v>8089</v>
       </c>
       <c r="Z5" t="n">
-        <v>426214</v>
+        <v>85507</v>
       </c>
       <c r="AA5" t="n">
-        <v>4005328</v>
+        <v>801659</v>
       </c>
       <c r="AB5" t="n">
-        <v>49808</v>
+        <v>9991</v>
       </c>
       <c r="AC5" t="n">
-        <v>145788</v>
+        <v>29239</v>
       </c>
       <c r="AD5" t="n">
-        <v>3165</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1072710</v>
+        <v>214636</v>
       </c>
       <c r="AG5" t="n">
-        <v>1476341</v>
+        <v>296450</v>
       </c>
       <c r="AH5" t="n">
-        <v>665240</v>
+        <v>133459</v>
       </c>
       <c r="AI5" t="n">
-        <v>151021</v>
+        <v>30288</v>
       </c>
       <c r="AJ5" t="n">
-        <v>250558</v>
+        <v>50141</v>
       </c>
       <c r="AK5" t="n">
-        <v>66400</v>
+        <v>13301</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735257625579834</v>
+        <v>0.9734619855880737</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643129110336304</v>
+        <v>0.964221715927124</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9838227033615112</v>
+        <v>0.9837768077850342</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963238835334778</v>
+        <v>0.9963127374649048</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9939071536064148</v>
+        <v>0.9938985705375671</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.998383641242981</v>
+        <v>0.9983823895454407</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>220</v>
+        <v>45</v>
       </c>
       <c r="D6" t="n">
-        <v>51634</v>
+        <v>15220</v>
       </c>
       <c r="E6" t="n">
-        <v>95549</v>
+        <v>18629</v>
       </c>
       <c r="F6" t="n">
-        <v>121162</v>
+        <v>28151</v>
       </c>
       <c r="G6" t="n">
-        <v>126564</v>
+        <v>16667</v>
       </c>
       <c r="H6" t="n">
-        <v>48851</v>
+        <v>9781</v>
       </c>
       <c r="I6" t="n">
-        <v>2600</v>
+        <v>926</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>32411</v>
+        <v>6517</v>
       </c>
       <c r="Z6" t="n">
-        <v>26831</v>
+        <v>5380</v>
       </c>
       <c r="AA6" t="n">
-        <v>54451</v>
+        <v>10917</v>
       </c>
       <c r="AB6" t="n">
-        <v>295559</v>
+        <v>59131</v>
       </c>
       <c r="AC6" t="n">
-        <v>34923</v>
+        <v>6993</v>
       </c>
       <c r="AD6" t="n">
-        <v>2405</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>106</v>
+        <v>20</v>
       </c>
       <c r="D7" t="n">
-        <v>455</v>
+        <v>365</v>
       </c>
       <c r="E7" t="n">
-        <v>43706</v>
+        <v>23440</v>
       </c>
       <c r="F7" t="n">
-        <v>285527</v>
+        <v>97965</v>
       </c>
       <c r="G7" t="n">
-        <v>220873</v>
+        <v>49054</v>
       </c>
       <c r="H7" t="n">
-        <v>1918019</v>
+        <v>314956</v>
       </c>
       <c r="I7" t="n">
-        <v>78166</v>
+        <v>23906</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>139</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>4056</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>148230</v>
+        <v>29666</v>
       </c>
       <c r="AB7" t="n">
-        <v>37923</v>
+        <v>7595</v>
       </c>
       <c r="AC7" t="n">
-        <v>2296294</v>
+        <v>459565</v>
       </c>
       <c r="AD7" t="n">
-        <v>60210</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>572</v>
+        <v>86</v>
       </c>
       <c r="D8" t="n">
-        <v>123</v>
+        <v>37</v>
       </c>
       <c r="E8" t="n">
-        <v>2041</v>
+        <v>1147</v>
       </c>
       <c r="F8" t="n">
-        <v>8885</v>
+        <v>4451</v>
       </c>
       <c r="G8" t="n">
-        <v>6719</v>
+        <v>2699</v>
       </c>
       <c r="H8" t="n">
-        <v>212740</v>
+        <v>59017</v>
       </c>
       <c r="I8" t="n">
-        <v>735505</v>
+        <v>125956</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>140</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>405</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>1651</v>
+        <v>331</v>
       </c>
       <c r="AB8" t="n">
-        <v>1327</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>62877</v>
+        <v>12595</v>
       </c>
       <c r="AD8" t="n">
-        <v>900185</v>
+        <v>180092</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
